--- a/system_design/Georgetown/V0.5.1/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5.1/bill_of_materials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/asifuzzaman_sc_edu/Documents/Github Repos/UAV-Deployable-Stage-Height-Sensor/system_design/Georgetown/V0.5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\UAV-Deployable-Stage-Height-Sensor\system_design\Georgetown\V0.5.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="111" documentId="13_ncr:1_{92FC9251-22EE-4CB6-81B0-D0434CABC585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{193EC476-6595-40B1-8D31-2A690007417A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A50012F-3208-4184-8D86-9642D7309BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -89,9 +89,6 @@
     <t>Total Cost</t>
   </si>
   <si>
-    <t>Component</t>
-  </si>
-  <si>
     <t>Amount</t>
   </si>
   <si>
@@ -434,9 +431,6 @@
     <t>SSA-104-W-T,  4 pin connector</t>
   </si>
   <si>
-    <t>PCB Designator</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 8GB Micro SD Card</t>
   </si>
   <si>
@@ -486,6 +480,12 @@
   </si>
   <si>
     <t>J1 (Lipo)</t>
+  </si>
+  <si>
+    <t>Part Designator</t>
+  </si>
+  <si>
+    <t>Detailed Component Name</t>
   </si>
 </sst>
 </file>
@@ -914,61 +914,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:L38"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="89.90625" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.54296875" customWidth="1"/>
-    <col min="5" max="5" width="13.08984375" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" customWidth="1"/>
-    <col min="7" max="7" width="69.453125" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="89.85546875" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="7" max="7" width="69.42578125" customWidth="1"/>
     <col min="8" max="8" width="76" customWidth="1"/>
-    <col min="9" max="9" width="83.54296875" customWidth="1"/>
-    <col min="10" max="10" width="62.54296875" customWidth="1"/>
-    <col min="11" max="11" width="55.81640625" customWidth="1"/>
+    <col min="9" max="9" width="83.5703125" customWidth="1"/>
+    <col min="10" max="10" width="62.5703125" customWidth="1"/>
+    <col min="11" max="11" width="55.85546875" customWidth="1"/>
     <col min="12" max="12" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>19</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>58</v>
-      </c>
       <c r="J1" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="L1" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -979,7 +979,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E2" s="3">
         <v>25.7</v>
@@ -989,27 +989,27 @@
         <v>25.7</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E3" s="3">
         <v>2.52</v>
@@ -1019,13 +1019,13 @@
         <v>2.52</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E4" s="3">
         <v>1.4</v>
@@ -1046,27 +1046,27 @@
         <v>1.4</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E5" s="3">
         <v>11.96</v>
@@ -1076,24 +1076,24 @@
         <v>11.96</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E6" s="3">
         <v>5.26</v>
@@ -1103,27 +1103,27 @@
         <v>5.26</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E7" s="3">
         <v>2.0299999999999998</v>
@@ -1133,16 +1133,16 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E8" s="3">
         <v>15.2</v>
@@ -1163,21 +1163,21 @@
         <v>15.2</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E9" s="3">
         <v>5.25</v>
@@ -1187,27 +1187,27 @@
         <v>5.25</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2">
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E10" s="3">
         <v>18</v>
@@ -1217,16 +1217,16 @@
         <v>18</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E11" s="3">
         <v>1.0900000000000001</v>
@@ -1247,15 +1247,15 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>9</v>
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E12" s="3">
         <v>0.57999999999999996</v>
@@ -1274,13 +1274,13 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
@@ -1291,7 +1291,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E13" s="3">
         <v>8.23</v>
@@ -1301,21 +1301,21 @@
         <v>8.23</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E14" s="3">
         <v>8.24</v>
@@ -1325,36 +1325,36 @@
         <v>8.24</v>
       </c>
       <c r="G14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="K14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="C15" s="2">
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E15" s="3">
         <v>2.0299999999999998</v>
@@ -1364,24 +1364,24 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C16" s="2">
         <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E16" s="3">
         <v>0.2</v>
@@ -1391,24 +1391,24 @@
         <v>0.2</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="2">
         <v>3</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E17" s="3">
         <v>0.1</v>
@@ -1418,24 +1418,24 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="2">
         <v>3</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E18" s="3">
         <v>0.1</v>
@@ -1445,24 +1445,24 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="2">
         <v>4</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E19" s="3">
         <v>0.1</v>
@@ -1472,15 +1472,15 @@
         <v>0.4</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
@@ -1489,7 +1489,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E20" s="3">
         <v>0.34</v>
@@ -1499,24 +1499,24 @@
         <v>0.34</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E21" s="3">
         <v>0.39</v>
@@ -1526,24 +1526,24 @@
         <v>0.39</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E22" s="3">
         <v>0.41</v>
@@ -1553,24 +1553,24 @@
         <v>0.41</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C23" s="2">
         <v>1</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E23" s="3">
         <v>0.26</v>
@@ -1580,24 +1580,24 @@
         <v>0.26</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C24" s="2">
         <v>4</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E24" s="3">
         <v>0.48</v>
@@ -1607,24 +1607,24 @@
         <v>1.92</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E25" s="3">
         <v>3.58</v>
@@ -1634,18 +1634,18 @@
         <v>3.58</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H25" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>14</v>
@@ -1654,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E26" s="3">
         <v>60.76</v>
@@ -1664,21 +1664,21 @@
         <v>60.76</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E27" s="3">
         <v>0.91</v>
@@ -1688,24 +1688,24 @@
         <v>0.91</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" s="2">
         <v>1</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E28" s="3">
         <v>2.15</v>
@@ -1715,24 +1715,24 @@
         <v>2.15</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="C29" s="2">
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E29" s="3">
         <v>0.1</v>
@@ -1742,21 +1742,21 @@
         <v>0.1</v>
       </c>
       <c r="G29" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="B30" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C30" s="2">
         <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E30" s="3">
         <v>0.13</v>
@@ -1766,24 +1766,24 @@
         <v>0.13</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" s="2">
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E31" s="3">
         <v>7.39</v>
@@ -1793,18 +1793,18 @@
         <v>66.509999999999991</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C32" s="2">
         <v>2</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E32" s="3">
         <v>0.01</v>
@@ -1815,15 +1815,15 @@
       </c>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C33" s="2">
         <v>2</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E33" s="3">
         <v>0.01</v>
@@ -1834,15 +1834,15 @@
       </c>
       <c r="G33" s="1"/>
     </row>
-    <row r="34" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C34" s="2">
         <v>2</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E34" s="3">
         <v>0.01</v>
@@ -1852,18 +1852,18 @@
         <v>0.02</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C35" s="2">
         <v>4</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E35" s="3">
         <v>7.2999999999999995E-2</v>
@@ -1873,21 +1873,21 @@
         <v>0.29199999999999998</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E36" s="3">
         <v>2.68</v>
@@ -1897,21 +1897,21 @@
         <v>2.68</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="C37" s="2">
         <v>1</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E37" s="3">
         <v>25</v>
@@ -1921,10 +1921,10 @@
         <v>25</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E38" s="4" t="s">
         <v>16</v>
       </c>
